--- a/data/trans_dic/P3A_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,01; 15,14</t>
+          <t>9,15; 15,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,06</t>
+          <t>5,92; 12,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,47</t>
+          <t>3,35; 8,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 9,47</t>
+          <t>5,5; 9,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 14,22</t>
+          <t>7,07; 14,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 11,03</t>
+          <t>4,99; 11,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,37</t>
+          <t>3,67; 9,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,56</t>
+          <t>5,5; 9,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,06; 13,47</t>
+          <t>8,92; 13,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,55</t>
+          <t>6,23; 10,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,65</t>
+          <t>4,0; 7,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,7</t>
+          <t>5,87; 8,75</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,35</t>
+          <t>3,14; 8,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,48</t>
+          <t>2,82; 7,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,79</t>
+          <t>1,24; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,79</t>
+          <t>2,51; 6,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,17</t>
+          <t>2,28; 6,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,86</t>
+          <t>2,94; 8,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,02</t>
+          <t>0,83; 4,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,26</t>
+          <t>3,09; 6,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,27</t>
+          <t>3,01; 6,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,24; 6,98</t>
+          <t>3,26; 6,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,95</t>
+          <t>1,38; 3,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,48</t>
+          <t>3,08; 5,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,28</t>
+          <t>1,37; 4,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,84</t>
+          <t>1,46; 4,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,27</t>
+          <t>0,81; 3,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,2</t>
+          <t>0,69; 4,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,3</t>
+          <t>0,65; 6,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,49</t>
+          <t>2,06; 7,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,89</t>
+          <t>0,59; 5,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,4</t>
+          <t>4,55; 10,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,93</t>
+          <t>1,5; 4,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,26</t>
+          <t>1,89; 4,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,02</t>
+          <t>0,96; 3,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,95</t>
+          <t>1,35; 5,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,8</t>
+          <t>1,35; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,61</t>
+          <t>1,66; 3,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,69</t>
+          <t>1,18; 2,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,25</t>
+          <t>3,54; 6,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,35</t>
+          <t>0,54; 2,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,94</t>
+          <t>0,74; 2,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,08</t>
+          <t>0,92; 3,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,76</t>
+          <t>1,41; 3,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,37</t>
+          <t>1,17; 2,31</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,92</t>
+          <t>1,46; 2,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,53</t>
+          <t>1,26; 2,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,72</t>
+          <t>2,52; 4,66</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,07</t>
+          <t>0,49; 2,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,69</t>
+          <t>2,77; 6,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,6</t>
+          <t>1,36; 3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,69</t>
+          <t>2,54; 5,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,18</t>
+          <t>0,82; 3,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,47</t>
+          <t>1,98; 4,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,4</t>
+          <t>0,56; 2,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,41</t>
+          <t>3,8; 6,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,57</t>
+          <t>0,86; 2,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,9</t>
+          <t>2,6; 4,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,57</t>
+          <t>1,16; 2,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 5,66</t>
+          <t>3,63; 5,69</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,34</t>
+          <t>3,0; 7,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,32</t>
+          <t>1,1; 4,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,16</t>
+          <t>0,7; 4,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 11,68</t>
+          <t>0,61; 8,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,03</t>
+          <t>2,11; 4,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,49</t>
+          <t>5,39; 8,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,26</t>
+          <t>3,4; 6,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,43; 9,64</t>
+          <t>6,49; 9,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,42</t>
+          <t>2,53; 4,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,37</t>
+          <t>4,77; 7,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,45</t>
+          <t>3,02; 5,46</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 8,6</t>
+          <t>5,5; 8,57</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 4,8</t>
+          <t>3,45; 4,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,65</t>
+          <t>3,2; 4,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,96</t>
+          <t>1,97; 3,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 5,19</t>
+          <t>3,31; 5,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 3,83</t>
+          <t>2,61; 3,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 5,38</t>
+          <t>3,85; 5,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,78</t>
+          <t>2,4; 3,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,06</t>
+          <t>4,44; 6,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,08</t>
+          <t>3,18; 4,06</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,72; 4,7</t>
+          <t>3,71; 4,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,18</t>
+          <t>2,34; 3,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,39</t>
+          <t>4,16; 5,39</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente una persona con remuneración (por ingresos del hogar o no) (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42620; 71575</t>
+          <t>43275; 71865</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>27343; 52713</t>
+          <t>25888; 53099</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14766; 36281</t>
+          <t>14330; 34950</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26849; 47828</t>
+          <t>27766; 47789</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22138; 43620</t>
+          <t>21691; 45222</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15226; 34695</t>
+          <t>15699; 34779</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12791; 32516</t>
+          <t>12745; 32113</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23914; 42691</t>
+          <t>24584; 41715</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>70625; 105004</t>
+          <t>69554; 105365</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46802; 79306</t>
+          <t>46814; 78269</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31720; 59279</t>
+          <t>31024; 59204</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55308; 82842</t>
+          <t>55928; 83338</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11600; 30651</t>
+          <t>11519; 30551</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11648; 31338</t>
+          <t>11829; 30406</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4723; 18077</t>
+          <t>4688; 17532</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11535; 26170</t>
+          <t>11360; 28042</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8762; 22941</t>
+          <t>8480; 24382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10011; 29936</t>
+          <t>9921; 28619</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3447; 18672</t>
+          <t>3103; 17153</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11829; 23962</t>
+          <t>11822; 23712</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22922; 46335</t>
+          <t>22204; 45976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24488; 52796</t>
+          <t>24638; 51871</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10561; 29636</t>
+          <t>10377; 28656</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26019; 45738</t>
+          <t>25664; 44981</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7536; 23220</t>
+          <t>7444; 24326</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8990; 24167</t>
+          <t>9211; 25668</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4361; 17004</t>
+          <t>4210; 16515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4297; 28057</t>
+          <t>4599; 28551</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1064; 10566</t>
+          <t>1095; 10900</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5370; 19473</t>
+          <t>5356; 19656</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>976; 9777</t>
+          <t>979; 9814</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7616; 17299</t>
+          <t>7562; 18017</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11038; 27922</t>
+          <t>10667; 28738</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17110; 37917</t>
+          <t>16825; 37334</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6324; 20708</t>
+          <t>6564; 20812</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10251; 41289</t>
+          <t>11260; 42832</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16409; 34633</t>
+          <t>16672; 35918</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18906; 41799</t>
+          <t>19209; 42567</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13408; 30795</t>
+          <t>13555; 30225</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36592; 64721</t>
+          <t>36652; 64536</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4471; 16777</t>
+          <t>3838; 15995</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5599; 22468</t>
+          <t>5696; 22685</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7198; 25301</t>
+          <t>7551; 25674</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13652; 36824</t>
+          <t>13769; 35858</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24266; 46189</t>
+          <t>22762; 45110</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28401; 56180</t>
+          <t>28077; 55086</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24283; 49782</t>
+          <t>24772; 48430</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52650; 95024</t>
+          <t>50631; 93795</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1714; 10766</t>
+          <t>1704; 10184</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15273; 34091</t>
+          <t>14106; 33641</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8284; 22329</t>
+          <t>8471; 22265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12195; 27021</t>
+          <t>12065; 27039</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5074; 18064</t>
+          <t>4676; 18479</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14599; 34063</t>
+          <t>15074; 33854</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4050; 17667</t>
+          <t>4135; 17705</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31538; 53891</t>
+          <t>31981; 54527</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7869; 23590</t>
+          <t>7903; 24188</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>34187; 62321</t>
+          <t>32995; 59431</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14829; 34897</t>
+          <t>15699; 36109</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48853; 74451</t>
+          <t>47765; 74918</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9034; 24863</t>
+          <t>8950; 23342</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3027; 14190</t>
+          <t>2929; 13165</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1831; 11873</t>
+          <t>1997; 11926</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2076; 28092</t>
+          <t>1474; 21459</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26462; 50156</t>
+          <t>26271; 51775</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59490; 94216</t>
+          <t>59847; 93602</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36465; 67736</t>
+          <t>36752; 67667</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>48948; 73393</t>
+          <t>49404; 73695</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>40162; 68178</t>
+          <t>39066; 67455</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65848; 101470</t>
+          <t>65591; 100546</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41862; 74560</t>
+          <t>41346; 74633</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>53793; 86159</t>
+          <t>55124; 85817</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>111156; 156837</t>
+          <t>112882; 156326</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>112072; 159009</t>
+          <t>109493; 154661</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65147; 100065</t>
+          <t>66651; 101393</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114554; 175210</t>
+          <t>111672; 172268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>86911; 129269</t>
+          <t>88095; 129519</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>136257; 190935</t>
+          <t>136514; 187799</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>87320; 133451</t>
+          <t>84810; 132792</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>155154; 216803</t>
+          <t>158670; 217074</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>208505; 271183</t>
+          <t>211550; 269579</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>258950; 327718</t>
+          <t>258680; 329352</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>160304; 219518</t>
+          <t>161585; 219834</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>283406; 374454</t>
+          <t>289395; 375010</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 15,2</t>
+          <t>9,0; 14,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,14</t>
+          <t>6,24; 11,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,16</t>
+          <t>3,28; 8,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,46</t>
+          <t>5,35; 9,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 14,75</t>
+          <t>7,02; 14,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 11,06</t>
+          <t>4,9; 10,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,25</t>
+          <t>3,58; 9,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,34</t>
+          <t>5,52; 9,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,52</t>
+          <t>9,05; 13,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 10,41</t>
+          <t>6,28; 10,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,64</t>
+          <t>3,98; 7,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,75</t>
+          <t>5,94; 8,76</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,33</t>
+          <t>2,97; 8,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,26</t>
+          <t>2,82; 7,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,65</t>
+          <t>1,25; 4,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,21</t>
+          <t>2,5; 6,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,56</t>
+          <t>2,15; 6,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,47</t>
+          <t>2,9; 8,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,61</t>
+          <t>1,06; 4,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,2</t>
+          <t>3,45; 6,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,01; 6,22</t>
+          <t>3,14; 6,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,26; 6,85</t>
+          <t>3,41; 6,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,82</t>
+          <t>1,32; 3,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,39</t>
+          <t>3,23; 5,68</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,48</t>
+          <t>1,35; 4,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,08</t>
+          <t>1,47; 3,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,18</t>
+          <t>0,82; 3,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,27</t>
+          <t>2,61; 6,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,5</t>
+          <t>0,66; 5,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,56</t>
+          <t>2,16; 7,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,91</t>
+          <t>0,58; 5,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,83</t>
+          <t>4,9; 11,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,05</t>
+          <t>1,47; 3,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,2</t>
+          <t>1,96; 4,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,03</t>
+          <t>1,04; 3,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,13</t>
+          <t>3,83; 6,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,9</t>
+          <t>1,32; 2,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,67</t>
+          <t>1,64; 3,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,64</t>
+          <t>1,23; 2,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 6,24</t>
+          <t>3,57; 6,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,24</t>
+          <t>0,64; 2,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,97</t>
+          <t>0,81; 2,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,12</t>
+          <t>0,97; 3,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,67</t>
+          <t>2,46; 4,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,31</t>
+          <t>1,19; 2,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,86</t>
+          <t>1,55; 2,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,46</t>
+          <t>1,26; 2,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,66</t>
+          <t>3,35; 5,01</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,91</t>
+          <t>0,46; 2,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,6</t>
+          <t>2,76; 6,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,59</t>
+          <t>1,36; 3,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,69</t>
+          <t>2,29; 5,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,25</t>
+          <t>0,88; 3,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,45</t>
+          <t>1,9; 4,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,4</t>
+          <t>0,61; 2,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,48</t>
+          <t>4,61; 6,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,63</t>
+          <t>0,89; 2,65</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,68</t>
+          <t>2,58; 4,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,66</t>
+          <t>1,15; 2,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,69</t>
+          <t>3,9; 5,68</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,83</t>
+          <t>2,88; 7,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,93</t>
+          <t>1,15; 5,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,18</t>
+          <t>0,7; 4,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 8,92</t>
+          <t>0,44; 9,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,16</t>
+          <t>2,17; 4,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,44</t>
+          <t>5,4; 8,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,25</t>
+          <t>3,34; 6,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,49; 9,68</t>
+          <t>6,19; 9,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,37</t>
+          <t>2,61; 4,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,31</t>
+          <t>4,74; 7,33</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,46</t>
+          <t>2,99; 5,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,5; 8,57</t>
+          <t>5,4; 8,24</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 4,78</t>
+          <t>3,44; 4,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,52</t>
+          <t>3,19; 4,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,0</t>
+          <t>1,95; 3,09</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,1</t>
+          <t>3,91; 5,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,84</t>
+          <t>2,58; 3,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,29</t>
+          <t>3,9; 5,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,77</t>
+          <t>2,42; 3,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,07</t>
+          <t>5,16; 6,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,06</t>
+          <t>3,14; 4,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,73</t>
+          <t>3,72; 4,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,18</t>
+          <t>2,36; 3,21</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,16; 5,39</t>
+          <t>4,74; 5,68</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>39099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32251</t>
+          <t>35513</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>74612</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43275; 71865</t>
+          <t>42537; 69860</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>25888; 53099</t>
+          <t>27277; 51810</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14330; 34950</t>
+          <t>14063; 35009</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27766; 47789</t>
+          <t>29452; 51956</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21691; 45222</t>
+          <t>21514; 44256</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15699; 34779</t>
+          <t>15417; 34170</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12745; 32113</t>
+          <t>12441; 32866</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24584; 41715</t>
+          <t>26909; 46196</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>69554; 105365</t>
+          <t>70557; 103899</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>46814; 78269</t>
+          <t>47231; 79258</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31024; 59204</t>
+          <t>30886; 58505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>55928; 83338</t>
+          <t>61629; 90926</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18050</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34981</t>
+          <t>40222</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11519; 30551</t>
+          <t>10899; 31206</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11829; 30406</t>
+          <t>11822; 29368</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4688; 17532</t>
+          <t>4712; 17552</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11360; 28042</t>
+          <t>12057; 28979</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8480; 24382</t>
+          <t>7991; 23000</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9921; 28619</t>
+          <t>9811; 30243</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3103; 17153</t>
+          <t>3940; 17722</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11822; 23712</t>
+          <t>14609; 29159</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22204; 45976</t>
+          <t>23221; 47560</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24638; 51871</t>
+          <t>25781; 52558</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10377; 28656</t>
+          <t>9913; 28897</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25664; 44981</t>
+          <t>29267; 51429</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11892</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>32956</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7444; 24326</t>
+          <t>7341; 23020</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9211; 25668</t>
+          <t>9226; 24767</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4210; 16515</t>
+          <t>4244; 15881</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4599; 28551</t>
+          <t>12310; 29146</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1095; 10900</t>
+          <t>1104; 9726</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5356; 19656</t>
+          <t>5622; 18723</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>979; 9814</t>
+          <t>970; 9359</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7562; 18017</t>
+          <t>9161; 21039</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10667; 28738</t>
+          <t>10420; 27773</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16825; 37334</t>
+          <t>17433; 38273</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6564; 20812</t>
+          <t>7165; 21041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11260; 42832</t>
+          <t>25195; 45446</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48858</t>
+          <t>52913</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25904</t>
+          <t>28218</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>74762</t>
+          <t>81131</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16672; 35918</t>
+          <t>16290; 35622</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19209; 42567</t>
+          <t>18951; 40099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13555; 30225</t>
+          <t>14030; 32144</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36652; 64536</t>
+          <t>40407; 71089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3838; 15995</t>
+          <t>4578; 15316</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5696; 22685</t>
+          <t>6164; 22321</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7551; 25674</t>
+          <t>7959; 26167</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13769; 35858</t>
+          <t>21191; 36520</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22762; 45110</t>
+          <t>23312; 44431</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28077; 55086</t>
+          <t>29757; 56673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24772; 48430</t>
+          <t>24836; 49392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50631; 93795</t>
+          <t>66842; 99850</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17958</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43953</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>66109</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1704; 10184</t>
+          <t>1623; 9993</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14106; 33641</t>
+          <t>14051; 34581</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8471; 22265</t>
+          <t>8430; 22659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12065; 27039</t>
+          <t>13017; 28510</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4676; 18479</t>
+          <t>4984; 17778</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15074; 33854</t>
+          <t>14478; 33538</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4135; 17705</t>
+          <t>4485; 17588</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>31981; 54527</t>
+          <t>38271; 57199</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7903; 24188</t>
+          <t>8217; 24330</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32995; 59431</t>
+          <t>32770; 60384</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15699; 36109</t>
+          <t>15612; 35665</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>47765; 74918</t>
+          <t>54563; 79450</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>59990</t>
+          <t>64250</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>67963</t>
+          <t>71915</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8950; 23342</t>
+          <t>8584; 23482</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2929; 13165</t>
+          <t>3069; 13834</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1997; 11926</t>
+          <t>1984; 12190</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1474; 21459</t>
+          <t>1035; 22115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>26271; 51775</t>
+          <t>26991; 52894</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59847; 93602</t>
+          <t>59869; 93510</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36752; 67667</t>
+          <t>36091; 67506</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>49404; 73695</t>
+          <t>52267; 78422</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39066; 67455</t>
+          <t>40230; 69596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65591; 100546</t>
+          <t>65254; 100918</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41346; 74633</t>
+          <t>40869; 73921</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>55124; 85817</t>
+          <t>58378; 89113</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>144798</t>
+          <t>157053</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>190921</t>
+          <t>209892</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>335720</t>
+          <t>366945</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>112882; 156326</t>
+          <t>112325; 157145</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>109493; 154661</t>
+          <t>108965; 154340</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66651; 101393</t>
+          <t>66011; 104279</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>111672; 172268</t>
+          <t>134453; 182303</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>88095; 129519</t>
+          <t>87199; 130077</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>136514; 187799</t>
+          <t>138353; 190124</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>84810; 132792</t>
+          <t>85406; 133531</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>158670; 217074</t>
+          <t>187436; 232055</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>211550; 269579</t>
+          <t>208863; 272786</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>258680; 329352</t>
+          <t>259272; 330945</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>161585; 219834</t>
+          <t>163029; 221919</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>289395; 375010</t>
+          <t>335311; 402182</t>
         </is>
       </c>
     </row>
